--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
@@ -5006,7 +5006,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
@@ -5006,7 +5006,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
@@ -5006,7 +5006,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
@@ -7072,7 +7072,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
@@ -7072,7 +7072,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251016_201510.xlsx
@@ -5006,7 +5006,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
